--- a/quizzes/peinture-18e-niveau2.xlsx
+++ b/quizzes/peinture-18e-niveau2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3812C47D-1FEB-494F-B94D-3277490624A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A492E1-5BBE-4383-85CE-CF3A512BD4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D010EE7-3957-4632-B43B-1193B29575F7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="263">
   <si>
     <t>image</t>
   </si>
@@ -83,9 +83,6 @@
     <t>1739</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1742</t>
   </si>
   <si>
@@ -128,9 +125,6 @@
     <t>La Raie</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/3/35/Jacques-Louis_David%2C_Le_Serment_des_Horaces.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Jacques-Louis David</t>
   </si>
   <si>
@@ -140,9 +134,6 @@
     <t>Le Serment des Horaces</t>
   </si>
   <si>
-    <t>Élisabeth Vigée Le Brun</t>
-  </si>
-  <si>
     <t>1787</t>
   </si>
   <si>
@@ -242,9 +233,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/f/f3/Jean-Baptiste_Greuze_-_The_Village_Agreement.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/e/ec/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UK.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/5/52/Thomas_Gainsborough_-_Mr_and_Mrs_Andrews.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -266,9 +254,6 @@
     <t>1762</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Johann Zoffany</t>
   </si>
   <si>
@@ -323,9 +308,6 @@
     <t>Watson and the Shark</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/d8/John_Singleton_Copley_-_Watson_and_the_Shark_%281778%29_-_NGA_Washington.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Richard Wilson</t>
   </si>
   <si>
@@ -368,9 +350,6 @@
     <t>Museo del Prado, Madrid</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Canaletto</t>
   </si>
   <si>
@@ -392,9 +371,6 @@
     <t>Musée des Beaux-Arts, Houston</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/1/10/Ca%27_Rezzonico_-_Il_rinoceronte_1751_-_Pietro_Longhi_.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Pietro Longhi</t>
   </si>
   <si>
@@ -425,9 +401,6 @@
     <t>Pompeo Batoni</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/d5/Pompeo_Batoni_-_Emperor_Joseph_II_with_Grand_Duke_Pietro_Leopoldo_of_Tuscany_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1769</t>
   </si>
   <si>
@@ -446,9 +419,6 @@
     <t>Vue de Dresde depuis la rive droite de l'Elbe</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/d5/El_Quitasol_%28Goya%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Francisco de Goya</t>
   </si>
   <si>
@@ -476,9 +446,6 @@
     <t>Le Parnasse</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/5/56/John_Henry_Fuseli_-_The_Nightmare.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Henry Fuseli</t>
   </si>
   <si>
@@ -530,9 +497,6 @@
     <t>Portrait des sœurs Gagarine</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/b/ba/La_Dame_au_voile_Alexander_Roslin_Stockholm.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Alexander Roslin</t>
   </si>
   <si>
@@ -554,9 +518,6 @@
     <t>La Mort du général Wolfe</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/a4/Gilbert_Stuart_-_George_Washington_%28Lansdowne_Portrait%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Gilbert Stuart</t>
   </si>
   <si>
@@ -578,9 +539,6 @@
     <t>Portrait de Benjamin Franklin</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/d4/The_Qianlong_Emperor_in_Ceremonial_Armour_on_Horseback.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Giuseppe Castiglione (Lang Shining)</t>
   </si>
   <si>
@@ -665,9 +623,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/4/42/Charles-Andr%C3%A9%2C_dit_Carle_Vanloo_-_Halte_de_chasse_%281737%29.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Carle Van Loo</t>
-  </si>
-  <si>
     <t>1737</t>
   </si>
   <si>
@@ -707,9 +662,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/8/8a/Ad%C3%A9la%C3%AFde_Labille-Guiard_-_Self-Portrait_with_Two_Pupils_-_The_Metropolitan_Museum_of_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Adélaïde Labille-Guiard</t>
-  </si>
-  <si>
     <t>Autoportrait avec deux élèves</t>
   </si>
   <si>
@@ -722,9 +674,6 @@
     <t>Portrait de George III</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/2/29/An_Experiment_on_a_bird_in_an_air_pump_1768_Joseph_Wright_of_Derby_-_54977535687.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Joseph Wright of Derby</t>
   </si>
   <si>
@@ -767,9 +716,6 @@
     <t>1761-1765</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/a7/It%C5%8D_Jakuch%C5%AB_-_Shells_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Coquillages</t>
   </si>
   <si>
@@ -812,7 +758,76 @@
     <t>Paysage avec villa d'été</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/b/b3/Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d4/The_Qianlong_Emperor_in_Ceremonial_Armour_on_Horseback.jpg/960px-The_Qianlong_Emperor_in_Ceremonial_Armour_on_Horseback.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d5/El_Quitasol_%28Goya%29.jpg/1280px-El_Quitasol_%28Goya%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f4/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg/1280px-Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/22/An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg/1280px-An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg/1280px-Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/33/Pompeo_Batoni_002.jpg/960px-Pompeo_Batoni_002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b3/Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg/960px-Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/John_Henry_Fuseli_-_The_Nightmare.JPG/1280px-John_Henry_Fuseli_-_The_Nightmare.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/ba/La_Dame_au_voile_Alexander_Roslin_Stockholm.jpg/960px-La_Dame_au_voile_Alexander_Roslin_Stockholm.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Ca%27_Rezzonico_-_Il_rinoceronte_1751_-_Pietro_Longhi_.jpg/960px-Ca%27_Rezzonico_-_Il_rinoceronte_1751_-_Pietro_Longhi_.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a3/Watsonandtheshark-original.jpg/1280px-Watsonandtheshark-original.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/75/Dmitry_Levitzky%2C_Denis_Diderot%2C_1773%2C_Mus%C3%A9e_d%27Art_et_Histoire_de_Gen%C3%A8ve_1829-0009.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Dmitri Levitzky</t>
+  </si>
+  <si>
+    <t>1773-1774</t>
+  </si>
+  <si>
+    <t>Musée d'art_et_d'histoire, Genève</t>
+  </si>
+  <si>
+    <t>Portrait de Denis Diderot</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg/960px-Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a7/It%C5%8D_Jakuch%C5%AB_-_Shells_%28Colorful_Realm_of_Living_Beings%29.jpg/960px-It%C5%8D_Jakuch%C5%AB_-_Shells_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg/1280px-Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Adélaïde LABILLE-GUIARD</t>
+  </si>
+  <si>
+    <t>Carle van LOO</t>
+  </si>
+  <si>
+    <t>Élisabeth VIGEE LE BRUN</t>
   </si>
 </sst>
 </file>
@@ -846,7 +861,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -857,6 +872,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC54F38"/>
         <bgColor rgb="FFC54F38"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -910,7 +931,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -926,6 +947,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1261,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172DCAAF-D19E-4ED4-B1CD-E8596A170419}">
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="51.28515625" customWidth="1"/>
@@ -1290,1013 +1313,1038 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>206</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>6</v>
+        <v>260</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>9</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>16</v>
+      <c r="A3" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>23</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="4" t="s">
-        <v>25</v>
+      <c r="A5" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>257</v>
+        <v>155</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>33</v>
+        <v>156</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>35</v>
+        <v>157</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>36</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>35</v>
-      </c>
       <c r="E10" s="5" t="s">
-        <v>45</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>67</v>
+        <v>164</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>54</v>
+        <v>163</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1789</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>55</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>61</v>
+      <c r="A12" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="4" t="s">
-        <v>63</v>
+        <v>213</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>62</v>
+        <v>214</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D13" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1783</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="5" t="s">
+      <c r="E19" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="D20" s="5" t="s">
-        <v>18</v>
+        <v>201</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>93</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>112</v>
+      <c r="A22" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A23" s="4" t="s">
-        <v>114</v>
+      <c r="A23" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C23" s="6">
-        <v>1783</v>
+        <v>98</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>120</v>
+      <c r="A24" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>125</v>
+      <c r="A25" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="4" t="s">
-        <v>128</v>
+      <c r="A26" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="4" t="s">
-        <v>132</v>
+      <c r="A27" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>44</v>
+        <v>171</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>126</v>
+        <v>234</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>137</v>
+      <c r="A28" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" s="5" t="s">
+      <c r="A29" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>140</v>
+      <c r="E29" s="8" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="4" t="s">
-        <v>141</v>
+        <v>5</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>142</v>
+        <v>6</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>143</v>
+        <v>8</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>144</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>145</v>
+        <v>63</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>146</v>
+        <v>35</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>147</v>
+        <v>36</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>148</v>
+        <v>8</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>149</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15.75" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>150</v>
+        <v>196</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>152</v>
+        <v>197</v>
+      </c>
+      <c r="C32" s="6">
+        <v>1721</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>153</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="4" t="s">
-        <v>156</v>
+        <v>203</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>155</v>
+        <v>204</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>157</v>
+        <v>39</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>158</v>
+        <v>205</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="4" t="s">
-        <v>160</v>
+        <v>24</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>159</v>
+        <v>25</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>161</v>
+        <v>26</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>162</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="4" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>165</v>
+        <v>118</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="4" t="s">
-        <v>167</v>
+        <v>18</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>168</v>
+        <v>19</v>
       </c>
       <c r="C36" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C38" s="6">
-        <v>1789</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>178</v>
+      <c r="D38" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>182</v>
+      <c r="A39" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>237</v>
+      <c r="A40" s="4" t="s">
+        <v>216</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>24</v>
+        <v>218</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>238</v>
+        <v>8</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E41" s="5" t="s">
+      <c r="A41" s="7" t="s">
         <v>243</v>
       </c>
+      <c r="B41" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>244</v>
+      <c r="A42" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>192</v>
+        <v>59</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>245</v>
+        <v>61</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>193</v>
+        <v>8</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>246</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>249</v>
+        <v>179</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>251</v>
+      <c r="A44" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="B44" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>252</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>253</v>
+      <c r="A45" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>187</v>
+        <v>129</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>186</v>
+        <v>8</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>254</v>
+        <v>130</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>240</v>
+        <v>23</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>256</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="4" t="s">
-        <v>195</v>
+      <c r="A47" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>196</v>
+        <v>45</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>198</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="4" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="C48" s="6">
         <v>1760</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="4" t="s">
-        <v>203</v>
+      <c r="A49" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>22</v>
+        <v>231</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="4" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C51" s="6">
-        <v>1721</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>213</v>
+      <c r="A51" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>217</v>
+      <c r="A52" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="4" t="s">
-        <v>218</v>
+      <c r="A53" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>219</v>
+        <v>89</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="4" t="s">
-        <v>221</v>
+        <v>113</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>222</v>
+        <v>114</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>11</v>
+        <v>116</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>223</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="4" t="s">
-        <v>224</v>
+      <c r="A55" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>225</v>
+        <v>65</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>226</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="4" t="s">
-        <v>227</v>
+        <v>149</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>228</v>
+        <v>148</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>92</v>
+        <v>150</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>229</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="4" t="s">
-        <v>230</v>
+      <c r="A57" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>231</v>
+        <v>54</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>56</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>232</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="4" t="s">
-        <v>233</v>
+      <c r="A58" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>234</v>
+        <v>174</v>
       </c>
       <c r="C58" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="5" t="s">
+      <c r="B59" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E59" s="5" t="s">
         <v>236</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E59">
+    <sortCondition ref="B2:B59"/>
+  </sortState>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{9FE834A6-ECEF-4986-A577-79A3855787E1}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{1177A6F2-E6B2-476E-A2A6-B0E82CDAA77D}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{1C8DD03B-57E2-4D5D-87A2-5BBA570E562A}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{9EB7565F-906C-4CAC-B7CA-7B2C2F95DC49}"/>
-    <hyperlink ref="A6" r:id="rId5" xr:uid="{050A610E-B724-4EF6-A305-61DFFF57E08C}"/>
-    <hyperlink ref="A13" r:id="rId6" xr:uid="{00B21B6F-99D8-4876-BED4-642AF6F093D2}"/>
-    <hyperlink ref="A8" r:id="rId7" xr:uid="{82552FB1-DCC4-41F5-8E8A-B3F6B05761BA}"/>
-    <hyperlink ref="A11" r:id="rId8" xr:uid="{68A68607-7EA8-4768-B5B9-A112A4C6A9EF}"/>
-    <hyperlink ref="A23" r:id="rId9" xr:uid="{C2FC4FCB-36AA-44D2-A09E-52D3A186110D}"/>
-    <hyperlink ref="A58" r:id="rId10" xr:uid="{AE735036-FC10-43F5-B7A2-146AE4BF1D92}"/>
-    <hyperlink ref="A57" r:id="rId11" xr:uid="{0928CFE6-F17E-4215-8C39-B1300F5CE1CE}"/>
-    <hyperlink ref="A56" r:id="rId12" xr:uid="{2562AA1A-2ED2-41BE-A099-5101BB438FB5}"/>
-    <hyperlink ref="A55" r:id="rId13" xr:uid="{1841E2B3-1652-4228-BB89-073BC65B4B0B}"/>
-    <hyperlink ref="A54" r:id="rId14" xr:uid="{30E3C83A-CD6D-4CFC-A8DD-1FFFDA3C7B75}"/>
-    <hyperlink ref="A53" r:id="rId15" xr:uid="{E78676A6-0F13-46A5-A761-078D37818DE3}"/>
-    <hyperlink ref="A52" r:id="rId16" xr:uid="{A4D9B011-E2D0-4F71-9F85-812FC62AF0B1}"/>
-    <hyperlink ref="A49" r:id="rId17" xr:uid="{E0E07521-79B5-4BA2-85D1-76F123D66818}"/>
-    <hyperlink ref="A50" r:id="rId18" xr:uid="{FF077238-8E52-4F74-960B-358EB2A3BE52}"/>
-    <hyperlink ref="A51" r:id="rId19" xr:uid="{A3EF0CD1-997F-4FAC-B51D-7AD79A3CFE12}"/>
-    <hyperlink ref="A48" r:id="rId20" xr:uid="{F9E663D2-51F8-4E47-8C07-7F22E6BE98DA}"/>
-    <hyperlink ref="A47" r:id="rId21" xr:uid="{7D74F484-FCBB-41D4-ADDF-CBFCEAFAC0AF}"/>
-    <hyperlink ref="A38" r:id="rId22" xr:uid="{D35537CC-09C0-46CA-BD40-743E457A622A}"/>
-    <hyperlink ref="A39" r:id="rId23" xr:uid="{393B41FC-3B90-4000-8910-1F773A2C2244}"/>
-    <hyperlink ref="A28" r:id="rId24" xr:uid="{4FFEF3FA-A758-444F-A755-C3C1C569C014}"/>
-    <hyperlink ref="A32" r:id="rId25" xr:uid="{3A0F49AD-7320-4748-A32D-C32C882A9C10}"/>
-    <hyperlink ref="A33" r:id="rId26" xr:uid="{C5077A97-8F71-4467-90B3-02343DACE3A4}"/>
-    <hyperlink ref="A34" r:id="rId27" xr:uid="{0F861FBE-7FF5-4B51-91C1-63A32EE6435F}"/>
-    <hyperlink ref="A35" r:id="rId28" xr:uid="{2D23B342-C714-4EF3-BBB2-0A8B3A4B5564}"/>
-    <hyperlink ref="A36" r:id="rId29" xr:uid="{A5D50A2F-BA88-4C06-8A5A-BC9406DFEE05}"/>
-    <hyperlink ref="A37" r:id="rId30" xr:uid="{F42374B4-D3A7-4EBD-A8FF-2BB134B8D437}"/>
-    <hyperlink ref="A29" r:id="rId31" xr:uid="{083AB9CA-F811-4290-8A7A-DD5442B9CAA0}"/>
-    <hyperlink ref="A30" r:id="rId32" xr:uid="{052C3565-C9B1-44B3-8B5D-F38676335856}"/>
-    <hyperlink ref="A31" r:id="rId33" xr:uid="{9608CD97-2B71-4393-BBDE-35018F637ED3}"/>
-    <hyperlink ref="A27" r:id="rId34" xr:uid="{61B462A0-2A6A-43E2-ABD2-AC2F299E1A2F}"/>
-    <hyperlink ref="A24" r:id="rId35" xr:uid="{4AF5ADFF-1ADB-4C17-969C-DB8FB9AA6271}"/>
-    <hyperlink ref="A25" r:id="rId36" xr:uid="{D02300E6-B445-47AF-97E4-7050501BFD07}"/>
-    <hyperlink ref="A26" r:id="rId37" xr:uid="{D41BE3A6-CFDA-4DD2-BE2D-40A241CB5ECA}"/>
-    <hyperlink ref="A7" r:id="rId38" xr:uid="{9E3FA052-CC3D-4324-80BE-C2D78C611A6F}"/>
+    <hyperlink ref="A30" r:id="rId1" xr:uid="{9FE834A6-ECEF-4986-A577-79A3855787E1}"/>
+    <hyperlink ref="A36" r:id="rId2" xr:uid="{1C8DD03B-57E2-4D5D-87A2-5BBA570E562A}"/>
+    <hyperlink ref="A34" r:id="rId3" xr:uid="{9EB7565F-906C-4CAC-B7CA-7B2C2F95DC49}"/>
+    <hyperlink ref="A42" r:id="rId4" xr:uid="{00B21B6F-99D8-4876-BED4-642AF6F093D2}"/>
+    <hyperlink ref="A31" r:id="rId5" xr:uid="{82552FB1-DCC4-41F5-8E8A-B3F6B05761BA}"/>
+    <hyperlink ref="A17" r:id="rId6" xr:uid="{C2FC4FCB-36AA-44D2-A09E-52D3A186110D}"/>
+    <hyperlink ref="A40" r:id="rId7" xr:uid="{AE735036-FC10-43F5-B7A2-146AE4BF1D92}"/>
+    <hyperlink ref="A13" r:id="rId8" xr:uid="{0928CFE6-F17E-4215-8C39-B1300F5CE1CE}"/>
+    <hyperlink ref="A4" r:id="rId9" xr:uid="{1841E2B3-1652-4228-BB89-073BC65B4B0B}"/>
+    <hyperlink ref="A2" r:id="rId10" xr:uid="{30E3C83A-CD6D-4CFC-A8DD-1FFFDA3C7B75}"/>
+    <hyperlink ref="A33" r:id="rId11" xr:uid="{E78676A6-0F13-46A5-A761-078D37818DE3}"/>
+    <hyperlink ref="A20" r:id="rId12" xr:uid="{A4D9B011-E2D0-4F71-9F85-812FC62AF0B1}"/>
+    <hyperlink ref="A50" r:id="rId13" xr:uid="{E0E07521-79B5-4BA2-85D1-76F123D66818}"/>
+    <hyperlink ref="A10" r:id="rId14" xr:uid="{FF077238-8E52-4F74-960B-358EB2A3BE52}"/>
+    <hyperlink ref="A32" r:id="rId15" xr:uid="{A3EF0CD1-997F-4FAC-B51D-7AD79A3CFE12}"/>
+    <hyperlink ref="A48" r:id="rId16" xr:uid="{F9E663D2-51F8-4E47-8C07-7F22E6BE98DA}"/>
+    <hyperlink ref="A44" r:id="rId17" xr:uid="{7D74F484-FCBB-41D4-ADDF-CBFCEAFAC0AF}"/>
+    <hyperlink ref="A11" r:id="rId18" xr:uid="{D35537CC-09C0-46CA-BD40-743E457A622A}"/>
+    <hyperlink ref="A35" r:id="rId19" xr:uid="{3A0F49AD-7320-4748-A32D-C32C882A9C10}"/>
+    <hyperlink ref="A16" r:id="rId20" xr:uid="{C5077A97-8F71-4467-90B3-02343DACE3A4}"/>
+    <hyperlink ref="A56" r:id="rId21" xr:uid="{0F861FBE-7FF5-4B51-91C1-63A32EE6435F}"/>
+    <hyperlink ref="A7" r:id="rId22" xr:uid="{A5D50A2F-BA88-4C06-8A5A-BC9406DFEE05}"/>
+    <hyperlink ref="A45" r:id="rId23" xr:uid="{083AB9CA-F811-4290-8A7A-DD5442B9CAA0}"/>
+    <hyperlink ref="A6" r:id="rId24" xr:uid="{052C3565-C9B1-44B3-8B5D-F38676335856}"/>
+    <hyperlink ref="A8" r:id="rId25" xr:uid="{61B462A0-2A6A-43E2-ABD2-AC2F299E1A2F}"/>
+    <hyperlink ref="A54" r:id="rId26" xr:uid="{D02300E6-B445-47AF-97E4-7050501BFD07}"/>
+    <hyperlink ref="A9" r:id="rId27" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F781F1A9-A8D6-4670-8C34-F9996210E288}"/>
+    <hyperlink ref="A24" r:id="rId28" xr:uid="{5D28D56E-465F-49A2-BFE2-9050D6005BBF}"/>
+    <hyperlink ref="A18" r:id="rId29" xr:uid="{0959804C-8A18-4FB8-A319-98F77423C1F1}"/>
+    <hyperlink ref="A12" r:id="rId30" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f4/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg/1280px-Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EC21EBC8-5FDA-466C-9BD7-FD6EEFDDDF49}"/>
+    <hyperlink ref="A41" r:id="rId31" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/22/An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg/1280px-An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D254D2A3-CB54-4743-967B-6D5A16550881}"/>
+    <hyperlink ref="A29" r:id="rId32" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg/1280px-Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{90BDDD29-D3A6-48BD-B0C7-0837F8F628A5}"/>
+    <hyperlink ref="A52" r:id="rId33" xr:uid="{51A95188-4B84-44AB-88E2-59C1DE9566FB}"/>
+    <hyperlink ref="A15" r:id="rId34" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b3/Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg/960px-Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{090F61DA-67F2-40F5-9072-B1CD1AE5C567}"/>
+    <hyperlink ref="A25" r:id="rId35" xr:uid="{00CA4BBD-B345-423A-BEB3-50AF2CDF3E69}"/>
+    <hyperlink ref="A3" r:id="rId36" xr:uid="{281FF5AD-CEBA-48C9-81C1-97FDA286D3F5}"/>
+    <hyperlink ref="A51" r:id="rId37" xr:uid="{C234852F-E558-43B5-B1F5-7C101E01F21F}"/>
+    <hyperlink ref="A39" r:id="rId38" xr:uid="{81BEE0C2-ED0B-4123-84E2-810D9592850D}"/>
+    <hyperlink ref="A14" r:id="rId39" xr:uid="{6344A05D-ABFF-4344-880A-B9F99F940A5F}"/>
+    <hyperlink ref="A22" r:id="rId40" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg/960px-Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FCFDF1FF-1CFE-4482-AA0E-36DDF8964994}"/>
+    <hyperlink ref="A28" r:id="rId41" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a7/It%C5%8D_Jakuch%C5%AB_-_Shells_%28Colorful_Realm_of_Living_Beings%29.jpg/960px-It%C5%8D_Jakuch%C5%AB_-_Shells_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9C6F0F8C-1B72-49E9-9F13-51A9D301AE5E}"/>
+    <hyperlink ref="A38" r:id="rId42" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg/1280px-Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1E99C6A6-D0F8-4BEA-95AE-50633C4BCE89}"/>
+    <hyperlink ref="A19" r:id="rId43" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BD7CA9DC-A7D9-45D1-AE63-FC00BBDB3AD4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-18e-niveau2.xlsx
+++ b/quizzes/peinture-18e-niveau2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A492E1-5BBE-4383-85CE-CF3A512BD4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC80C77-12DB-48EC-A1D6-5ADEEA47E614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D010EE7-3957-4632-B43B-1193B29575F7}"/>
   </bookViews>
@@ -56,9 +56,6 @@
     <t>titre de l’œuvre</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/2/28/L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Jean-Antoine Watteau</t>
   </si>
   <si>
@@ -828,6 +825,9 @@
   </si>
   <si>
     <t>Élisabeth VIGEE LE BRUN</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/28/L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg/1280px-L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -1313,988 +1313,988 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>153</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>209</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>157</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C11" s="6">
         <v>1789</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>214</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="C14" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="E14" s="8" t="s">
         <v>254</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C17" s="6">
         <v>1783</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B18" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>126</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>14</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B21" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B22" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="D22" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="E22" s="8" t="s">
         <v>161</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="14.25" customHeight="1">
       <c r="A23" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B24" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="8" t="s">
+      <c r="E24" s="8" t="s">
         <v>167</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B25" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="D25" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="E25" s="8" t="s">
         <v>137</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>169</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B28" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="E28" s="8" t="s">
         <v>224</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B29" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="D29" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="8" t="s">
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="8" t="s">
         <v>8</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B31" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15.75" customHeight="1">
       <c r="A32" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>196</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>197</v>
       </c>
       <c r="C32" s="6">
         <v>1721</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C33" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="C34" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="D34" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="D35" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>141</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="C36" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="E36" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B38" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="D38" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="E38" s="8" t="s">
         <v>73</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="C40" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="D40" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>218</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B41" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E41" s="8" t="s">
         <v>211</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C42" s="5" t="s">
+      <c r="D42" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="D43" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="E43" s="5" t="s">
         <v>227</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="C44" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="5" t="s">
+      <c r="E44" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="C45" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D46" s="5" t="s">
+      <c r="E46" s="5" t="s">
         <v>221</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B47" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E47" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>185</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>186</v>
       </c>
       <c r="C48" s="6">
         <v>1760</v>
       </c>
       <c r="D48" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="E48" s="5" t="s">
         <v>187</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C49" s="5" t="s">
+      <c r="D49" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="E49" s="5" t="s">
         <v>231</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="C50" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="D50" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" s="5" t="s">
         <v>191</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B51" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D51" s="8" t="s">
+      <c r="E51" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B52" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C52" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="D52" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="E52" s="8" t="s">
         <v>121</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B53" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E53" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B54" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="C54" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="D54" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="E54" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="C55" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="D55" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B56" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C56" s="5" t="s">
+      <c r="D56" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E56" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C57" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C57" s="5" t="s">
+      <c r="D57" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="E57" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E58" s="5" t="s">
         <v>237</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="E59" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -2302,49 +2302,49 @@
     <sortCondition ref="B2:B59"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="A30" r:id="rId1" xr:uid="{9FE834A6-ECEF-4986-A577-79A3855787E1}"/>
-    <hyperlink ref="A36" r:id="rId2" xr:uid="{1C8DD03B-57E2-4D5D-87A2-5BBA570E562A}"/>
-    <hyperlink ref="A34" r:id="rId3" xr:uid="{9EB7565F-906C-4CAC-B7CA-7B2C2F95DC49}"/>
-    <hyperlink ref="A42" r:id="rId4" xr:uid="{00B21B6F-99D8-4876-BED4-642AF6F093D2}"/>
-    <hyperlink ref="A31" r:id="rId5" xr:uid="{82552FB1-DCC4-41F5-8E8A-B3F6B05761BA}"/>
-    <hyperlink ref="A17" r:id="rId6" xr:uid="{C2FC4FCB-36AA-44D2-A09E-52D3A186110D}"/>
-    <hyperlink ref="A40" r:id="rId7" xr:uid="{AE735036-FC10-43F5-B7A2-146AE4BF1D92}"/>
-    <hyperlink ref="A13" r:id="rId8" xr:uid="{0928CFE6-F17E-4215-8C39-B1300F5CE1CE}"/>
-    <hyperlink ref="A4" r:id="rId9" xr:uid="{1841E2B3-1652-4228-BB89-073BC65B4B0B}"/>
-    <hyperlink ref="A2" r:id="rId10" xr:uid="{30E3C83A-CD6D-4CFC-A8DD-1FFFDA3C7B75}"/>
-    <hyperlink ref="A33" r:id="rId11" xr:uid="{E78676A6-0F13-46A5-A761-078D37818DE3}"/>
-    <hyperlink ref="A20" r:id="rId12" xr:uid="{A4D9B011-E2D0-4F71-9F85-812FC62AF0B1}"/>
-    <hyperlink ref="A50" r:id="rId13" xr:uid="{E0E07521-79B5-4BA2-85D1-76F123D66818}"/>
-    <hyperlink ref="A10" r:id="rId14" xr:uid="{FF077238-8E52-4F74-960B-358EB2A3BE52}"/>
-    <hyperlink ref="A32" r:id="rId15" xr:uid="{A3EF0CD1-997F-4FAC-B51D-7AD79A3CFE12}"/>
-    <hyperlink ref="A48" r:id="rId16" xr:uid="{F9E663D2-51F8-4E47-8C07-7F22E6BE98DA}"/>
-    <hyperlink ref="A44" r:id="rId17" xr:uid="{7D74F484-FCBB-41D4-ADDF-CBFCEAFAC0AF}"/>
-    <hyperlink ref="A11" r:id="rId18" xr:uid="{D35537CC-09C0-46CA-BD40-743E457A622A}"/>
-    <hyperlink ref="A35" r:id="rId19" xr:uid="{3A0F49AD-7320-4748-A32D-C32C882A9C10}"/>
-    <hyperlink ref="A16" r:id="rId20" xr:uid="{C5077A97-8F71-4467-90B3-02343DACE3A4}"/>
-    <hyperlink ref="A56" r:id="rId21" xr:uid="{0F861FBE-7FF5-4B51-91C1-63A32EE6435F}"/>
-    <hyperlink ref="A7" r:id="rId22" xr:uid="{A5D50A2F-BA88-4C06-8A5A-BC9406DFEE05}"/>
-    <hyperlink ref="A45" r:id="rId23" xr:uid="{083AB9CA-F811-4290-8A7A-DD5442B9CAA0}"/>
-    <hyperlink ref="A6" r:id="rId24" xr:uid="{052C3565-C9B1-44B3-8B5D-F38676335856}"/>
-    <hyperlink ref="A8" r:id="rId25" xr:uid="{61B462A0-2A6A-43E2-ABD2-AC2F299E1A2F}"/>
-    <hyperlink ref="A54" r:id="rId26" xr:uid="{D02300E6-B445-47AF-97E4-7050501BFD07}"/>
-    <hyperlink ref="A9" r:id="rId27" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F781F1A9-A8D6-4670-8C34-F9996210E288}"/>
-    <hyperlink ref="A24" r:id="rId28" xr:uid="{5D28D56E-465F-49A2-BFE2-9050D6005BBF}"/>
-    <hyperlink ref="A18" r:id="rId29" xr:uid="{0959804C-8A18-4FB8-A319-98F77423C1F1}"/>
-    <hyperlink ref="A12" r:id="rId30" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f4/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg/1280px-Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EC21EBC8-5FDA-466C-9BD7-FD6EEFDDDF49}"/>
-    <hyperlink ref="A41" r:id="rId31" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/22/An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg/1280px-An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D254D2A3-CB54-4743-967B-6D5A16550881}"/>
-    <hyperlink ref="A29" r:id="rId32" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg/1280px-Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{90BDDD29-D3A6-48BD-B0C7-0837F8F628A5}"/>
-    <hyperlink ref="A52" r:id="rId33" xr:uid="{51A95188-4B84-44AB-88E2-59C1DE9566FB}"/>
-    <hyperlink ref="A15" r:id="rId34" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b3/Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg/960px-Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{090F61DA-67F2-40F5-9072-B1CD1AE5C567}"/>
-    <hyperlink ref="A25" r:id="rId35" xr:uid="{00CA4BBD-B345-423A-BEB3-50AF2CDF3E69}"/>
-    <hyperlink ref="A3" r:id="rId36" xr:uid="{281FF5AD-CEBA-48C9-81C1-97FDA286D3F5}"/>
-    <hyperlink ref="A51" r:id="rId37" xr:uid="{C234852F-E558-43B5-B1F5-7C101E01F21F}"/>
-    <hyperlink ref="A39" r:id="rId38" xr:uid="{81BEE0C2-ED0B-4123-84E2-810D9592850D}"/>
-    <hyperlink ref="A14" r:id="rId39" xr:uid="{6344A05D-ABFF-4344-880A-B9F99F940A5F}"/>
-    <hyperlink ref="A22" r:id="rId40" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg/960px-Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FCFDF1FF-1CFE-4482-AA0E-36DDF8964994}"/>
-    <hyperlink ref="A28" r:id="rId41" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a7/It%C5%8D_Jakuch%C5%AB_-_Shells_%28Colorful_Realm_of_Living_Beings%29.jpg/960px-It%C5%8D_Jakuch%C5%AB_-_Shells_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9C6F0F8C-1B72-49E9-9F13-51A9D301AE5E}"/>
-    <hyperlink ref="A38" r:id="rId42" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg/1280px-Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1E99C6A6-D0F8-4BEA-95AE-50633C4BCE89}"/>
-    <hyperlink ref="A19" r:id="rId43" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BD7CA9DC-A7D9-45D1-AE63-FC00BBDB3AD4}"/>
+    <hyperlink ref="A36" r:id="rId1" xr:uid="{1C8DD03B-57E2-4D5D-87A2-5BBA570E562A}"/>
+    <hyperlink ref="A34" r:id="rId2" xr:uid="{9EB7565F-906C-4CAC-B7CA-7B2C2F95DC49}"/>
+    <hyperlink ref="A42" r:id="rId3" xr:uid="{00B21B6F-99D8-4876-BED4-642AF6F093D2}"/>
+    <hyperlink ref="A31" r:id="rId4" xr:uid="{82552FB1-DCC4-41F5-8E8A-B3F6B05761BA}"/>
+    <hyperlink ref="A17" r:id="rId5" xr:uid="{C2FC4FCB-36AA-44D2-A09E-52D3A186110D}"/>
+    <hyperlink ref="A40" r:id="rId6" xr:uid="{AE735036-FC10-43F5-B7A2-146AE4BF1D92}"/>
+    <hyperlink ref="A13" r:id="rId7" xr:uid="{0928CFE6-F17E-4215-8C39-B1300F5CE1CE}"/>
+    <hyperlink ref="A4" r:id="rId8" xr:uid="{1841E2B3-1652-4228-BB89-073BC65B4B0B}"/>
+    <hyperlink ref="A2" r:id="rId9" xr:uid="{30E3C83A-CD6D-4CFC-A8DD-1FFFDA3C7B75}"/>
+    <hyperlink ref="A33" r:id="rId10" xr:uid="{E78676A6-0F13-46A5-A761-078D37818DE3}"/>
+    <hyperlink ref="A20" r:id="rId11" xr:uid="{A4D9B011-E2D0-4F71-9F85-812FC62AF0B1}"/>
+    <hyperlink ref="A50" r:id="rId12" xr:uid="{E0E07521-79B5-4BA2-85D1-76F123D66818}"/>
+    <hyperlink ref="A10" r:id="rId13" xr:uid="{FF077238-8E52-4F74-960B-358EB2A3BE52}"/>
+    <hyperlink ref="A32" r:id="rId14" xr:uid="{A3EF0CD1-997F-4FAC-B51D-7AD79A3CFE12}"/>
+    <hyperlink ref="A48" r:id="rId15" xr:uid="{F9E663D2-51F8-4E47-8C07-7F22E6BE98DA}"/>
+    <hyperlink ref="A44" r:id="rId16" xr:uid="{7D74F484-FCBB-41D4-ADDF-CBFCEAFAC0AF}"/>
+    <hyperlink ref="A11" r:id="rId17" xr:uid="{D35537CC-09C0-46CA-BD40-743E457A622A}"/>
+    <hyperlink ref="A35" r:id="rId18" xr:uid="{3A0F49AD-7320-4748-A32D-C32C882A9C10}"/>
+    <hyperlink ref="A16" r:id="rId19" xr:uid="{C5077A97-8F71-4467-90B3-02343DACE3A4}"/>
+    <hyperlink ref="A56" r:id="rId20" xr:uid="{0F861FBE-7FF5-4B51-91C1-63A32EE6435F}"/>
+    <hyperlink ref="A7" r:id="rId21" xr:uid="{A5D50A2F-BA88-4C06-8A5A-BC9406DFEE05}"/>
+    <hyperlink ref="A45" r:id="rId22" xr:uid="{083AB9CA-F811-4290-8A7A-DD5442B9CAA0}"/>
+    <hyperlink ref="A6" r:id="rId23" xr:uid="{052C3565-C9B1-44B3-8B5D-F38676335856}"/>
+    <hyperlink ref="A8" r:id="rId24" xr:uid="{61B462A0-2A6A-43E2-ABD2-AC2F299E1A2F}"/>
+    <hyperlink ref="A54" r:id="rId25" xr:uid="{D02300E6-B445-47AF-97E4-7050501BFD07}"/>
+    <hyperlink ref="A9" r:id="rId26" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F781F1A9-A8D6-4670-8C34-F9996210E288}"/>
+    <hyperlink ref="A24" r:id="rId27" xr:uid="{5D28D56E-465F-49A2-BFE2-9050D6005BBF}"/>
+    <hyperlink ref="A18" r:id="rId28" xr:uid="{0959804C-8A18-4FB8-A319-98F77423C1F1}"/>
+    <hyperlink ref="A12" r:id="rId29" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f4/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg/1280px-Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EC21EBC8-5FDA-466C-9BD7-FD6EEFDDDF49}"/>
+    <hyperlink ref="A41" r:id="rId30" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/22/An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg/1280px-An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D254D2A3-CB54-4743-967B-6D5A16550881}"/>
+    <hyperlink ref="A29" r:id="rId31" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg/1280px-Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{90BDDD29-D3A6-48BD-B0C7-0837F8F628A5}"/>
+    <hyperlink ref="A52" r:id="rId32" xr:uid="{51A95188-4B84-44AB-88E2-59C1DE9566FB}"/>
+    <hyperlink ref="A15" r:id="rId33" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b3/Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg/960px-Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{090F61DA-67F2-40F5-9072-B1CD1AE5C567}"/>
+    <hyperlink ref="A25" r:id="rId34" xr:uid="{00CA4BBD-B345-423A-BEB3-50AF2CDF3E69}"/>
+    <hyperlink ref="A3" r:id="rId35" xr:uid="{281FF5AD-CEBA-48C9-81C1-97FDA286D3F5}"/>
+    <hyperlink ref="A51" r:id="rId36" xr:uid="{C234852F-E558-43B5-B1F5-7C101E01F21F}"/>
+    <hyperlink ref="A39" r:id="rId37" xr:uid="{81BEE0C2-ED0B-4123-84E2-810D9592850D}"/>
+    <hyperlink ref="A14" r:id="rId38" xr:uid="{6344A05D-ABFF-4344-880A-B9F99F940A5F}"/>
+    <hyperlink ref="A22" r:id="rId39" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg/960px-Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FCFDF1FF-1CFE-4482-AA0E-36DDF8964994}"/>
+    <hyperlink ref="A28" r:id="rId40" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a7/It%C5%8D_Jakuch%C5%AB_-_Shells_%28Colorful_Realm_of_Living_Beings%29.jpg/960px-It%C5%8D_Jakuch%C5%AB_-_Shells_%28Colorful_Realm_of_Living_Beings%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9C6F0F8C-1B72-49E9-9F13-51A9D301AE5E}"/>
+    <hyperlink ref="A38" r:id="rId41" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg/1280px-Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1E99C6A6-D0F8-4BEA-95AE-50633C4BCE89}"/>
+    <hyperlink ref="A19" r:id="rId42" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BD7CA9DC-A7D9-45D1-AE63-FC00BBDB3AD4}"/>
+    <hyperlink ref="A30" r:id="rId43" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/28/L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg/1280px-L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{30966001-D77B-428F-91B1-C8DEDEFABA19}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-18e-niveau2.xlsx
+++ b/quizzes/peinture-18e-niveau2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CE66536-FA20-48FB-B6F4-AD862ACD6439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AE45BF8-1B82-42ED-8189-11C837F6E90B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="366">
   <si>
     <t>image</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Dimensions</t>
   </si>
   <si>
+    <t>Nationalité</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/d/d3/Allan_Ramsay_-_Jean-Jacques_Rousseau_%281712_-_1778%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>75,9 × 62,9 cm</t>
   </si>
   <si>
+    <t>anglaise (Royaume-Uni)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/4/42/Kauffmann_Cornelia_mater_Gracchorum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -91,6 +97,9 @@
     <t>101,6 × 127 cm</t>
   </si>
   <si>
+    <t>suisse</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/f/f8/The_Death_of_General_Wolfe_B.West%2C1770.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -112,6 +121,9 @@
     <t>152,6 × 214,5 cm</t>
   </si>
   <si>
+    <t>américaine</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -133,6 +145,9 @@
     <t>125 × 204 cm</t>
   </si>
   <si>
+    <t>italienne</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/4/42/Charles-Andr%C3%A9%2C_dit_Carle_Vanloo_-_Halte_de_chasse_%281737%29.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -154,6 +169,9 @@
     <t>216 × 276 cm</t>
   </si>
   <si>
+    <t>française</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/4/4e/Deuxieme_vue_du_port_de_Bordeaux_prise_du_ch%C3%A2teau_Trompette.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -235,6 +253,9 @@
     <t>104 × 152 cm</t>
   </si>
   <si>
+    <t>espagnole</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -661,6 +682,9 @@
     <t>63 × 52 cm</t>
   </si>
   <si>
+    <t>suédoise</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/7/73/Anton_Raphael_Mengs_-_Parnassus_%28FondazioneTorlonia%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -682,6 +706,9 @@
     <t>dimensions architecturales</t>
   </si>
   <si>
+    <t>allemande</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/0/02/Canaletto_-_Dresden_seen_from_the_Right_Bank_of_the_Elbe%2C_beneath_the_Augusts_Bridge_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -859,6 +886,9 @@
     <t>76,2 × 63,5 cm</t>
   </si>
   <si>
+    <t>écossaise (Royaume-Uni)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fe/Jacques-Louis_David_002.jpg/960px-Jacques-Louis_David_002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
   </si>
   <si>
@@ -1070,6 +1100,9 @@
   </si>
   <si>
     <t>1757-1825</t>
+  </si>
+  <si>
+    <t>russe</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/d/dd/VAlfieriFabre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
@@ -1599,7 +1632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
@@ -1612,7 +1645,7 @@
     <col min="8" max="8" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="18" customFormat="1" ht="30" customHeight="1">
+    <row r="1" spans="1:9" s="18" customFormat="1" ht="30" customHeight="1">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1637,1539 +1670,1722 @@
       <c r="H1" s="24" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="I11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="I12" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="7" t="s">
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="I13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I14" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="7" t="s">
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="12" t="s">
+      <c r="E16" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="I16" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>122</v>
+      </c>
+      <c r="I17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>128</v>
+      </c>
+      <c r="I18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C19" s="10">
         <v>1721</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>134</v>
+      </c>
+      <c r="I19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="6" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>140</v>
+      </c>
+      <c r="I20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="6" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+        <v>145</v>
+      </c>
+      <c r="I21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+        <v>152</v>
+      </c>
+      <c r="I22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="6" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>158</v>
+      </c>
+      <c r="I23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="6" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+        <v>164</v>
+      </c>
+      <c r="I24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="7" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>171</v>
+      </c>
+      <c r="I25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="6" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>178</v>
+      </c>
+      <c r="I26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="7" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>184</v>
+      </c>
+      <c r="I27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="7" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>190</v>
+      </c>
+      <c r="I28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="6" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C29" s="11">
         <v>1794</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>197</v>
+      </c>
+      <c r="I29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="6" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C30" s="11">
         <v>1796</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+        <v>202</v>
+      </c>
+      <c r="I30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="6" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C31" s="11">
         <v>1791</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+        <v>207</v>
+      </c>
+      <c r="I31" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="2" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+        <v>213</v>
+      </c>
+      <c r="I32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="4" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+        <v>219</v>
+      </c>
+      <c r="I33" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="4" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>227</v>
+      </c>
+      <c r="I34" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="4" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>235</v>
+      </c>
+      <c r="I35" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="4" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+        <v>242</v>
+      </c>
+      <c r="I36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="4" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+        <v>235</v>
+      </c>
+      <c r="I37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="1" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>250</v>
+      </c>
+      <c r="I38" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="4" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>235</v>
+      </c>
+      <c r="I39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="4" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <v>257</v>
+      </c>
+      <c r="I40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" s="4" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+        <v>262</v>
+      </c>
+      <c r="I41" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="4" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+        <v>235</v>
+      </c>
+      <c r="I42" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="4" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>274</v>
+      </c>
+      <c r="I43" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="1" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <v>227</v>
+      </c>
+      <c r="I44" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="4" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+        <v>235</v>
+      </c>
+      <c r="I45" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="1" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>287</v>
+      </c>
+      <c r="I46" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="4" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+        <v>293</v>
+      </c>
+      <c r="I47" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="4" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E48" s="22" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <v>297</v>
+      </c>
+      <c r="I48" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="4" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+        <v>302</v>
+      </c>
+      <c r="I49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="4" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E50" s="22" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <v>305</v>
+      </c>
+      <c r="I50" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="4" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>235</v>
+      </c>
+      <c r="I51" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="4" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C52" s="14">
         <v>1771</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>314</v>
+      </c>
+      <c r="I52" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="4" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+        <v>321</v>
+      </c>
+      <c r="I53" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="4" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+        <v>325</v>
+      </c>
+      <c r="I54" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="1" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E55" s="22" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <v>235</v>
+      </c>
+      <c r="I55" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="4" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+        <v>337</v>
+      </c>
+      <c r="I56" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" s="4" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E57" s="22" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+        <v>235</v>
+      </c>
+      <c r="I57" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="4" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="E58" s="22" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+        <v>348</v>
+      </c>
+      <c r="I58" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" s="4" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+        <v>314</v>
+      </c>
+      <c r="I59" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" s="4" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+        <v>235</v>
+      </c>
+      <c r="I60" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="4" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="C61" s="5">
         <v>1794</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="E61" s="23" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>226</v>
+        <v>235</v>
+      </c>
+      <c r="I61" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
